--- a/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC6/GradeDetail.xlsx
+++ b/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC6/GradeDetail.xlsx
@@ -1137,7 +1137,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1196,7 +1196,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>49</x:v>
@@ -1249,7 +1249,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1305,7 +1305,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1364,7 +1364,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>49</x:v>
@@ -1420,7 +1420,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>49</x:v>
@@ -1473,7 +1473,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1532,7 +1532,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>66</x:v>
@@ -1588,7 +1588,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>49</x:v>
@@ -1641,7 +1641,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1697,7 +1697,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q12" s="0">
         <x:v>4000</x:v>
@@ -1753,7 +1753,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1812,7 +1812,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>49</x:v>
@@ -1865,7 +1865,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1921,7 +1921,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1980,7 +1980,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>49</x:v>
@@ -2036,7 +2036,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="R18" s="2" t="s">
         <x:v>49</x:v>
@@ -2089,7 +2089,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="Q19" s="0">
         <x:v>4000</x:v>
@@ -2148,7 +2148,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>66</x:v>
@@ -2204,7 +2204,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>49</x:v>
@@ -2257,7 +2257,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>57710</x:v>
+        <x:v>52756</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
@@ -2369,7 +2369,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P24" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q24" s="0">
         <x:v>4000</x:v>
@@ -2428,7 +2428,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q25" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R25" s="5" t="s">
         <x:v>71</x:v>
@@ -2481,7 +2481,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="P26" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q26" s="0">
         <x:v>4000</x:v>
@@ -2540,7 +2540,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q27" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R27" s="5" t="s">
         <x:v>71</x:v>
@@ -2596,7 +2596,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q28" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R28" s="5" t="s">
         <x:v>71</x:v>
@@ -2649,7 +2649,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q29" s="0">
         <x:v>4000</x:v>
@@ -2708,7 +2708,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q30" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R30" s="5" t="s">
         <x:v>71</x:v>
@@ -2761,7 +2761,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P31" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q31" s="0">
         <x:v>4000</x:v>
@@ -2820,7 +2820,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q32" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R32" s="5" t="s">
         <x:v>71</x:v>
@@ -2873,7 +2873,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P33" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q33" s="0">
         <x:v>4000</x:v>
@@ -2932,7 +2932,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q34" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R34" s="5" t="s">
         <x:v>71</x:v>
@@ -2985,7 +2985,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P35" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q35" s="0">
         <x:v>4000</x:v>
@@ -3041,7 +3041,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="P36" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q36" s="0">
         <x:v>4000</x:v>
@@ -3100,7 +3100,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q37" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R37" s="5" t="s">
         <x:v>71</x:v>
@@ -3156,7 +3156,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q38" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R38" s="5" t="s">
         <x:v>71</x:v>
@@ -3209,7 +3209,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P39" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q39" s="0">
         <x:v>4000</x:v>
@@ -3268,7 +3268,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q40" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R40" s="5" t="s">
         <x:v>71</x:v>
@@ -3321,7 +3321,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P41" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q41" s="0">
         <x:v>4000</x:v>
@@ -3380,7 +3380,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q42" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R42" s="5" t="s">
         <x:v>71</x:v>
@@ -3433,7 +3433,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P43" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q43" s="0">
         <x:v>4000</x:v>
@@ -3492,7 +3492,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q44" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R44" s="5" t="s">
         <x:v>71</x:v>
@@ -3545,7 +3545,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P45" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q45" s="0">
         <x:v>4000</x:v>
@@ -3601,7 +3601,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="P46" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q46" s="0">
         <x:v>4000</x:v>
@@ -3660,7 +3660,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q47" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R47" s="5" t="s">
         <x:v>71</x:v>
@@ -3716,7 +3716,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q48" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R48" s="5" t="s">
         <x:v>71</x:v>
@@ -3769,7 +3769,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P49" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q49" s="0">
         <x:v>4000</x:v>
@@ -3828,7 +3828,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q50" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R50" s="5" t="s">
         <x:v>71</x:v>
@@ -3881,7 +3881,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P51" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="Q51" s="0">
         <x:v>4000</x:v>
@@ -3940,7 +3940,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q52" s="0">
-        <x:v>39724</x:v>
+        <x:v>55074</x:v>
       </x:c>
       <x:c r="R52" s="5" t="s">
         <x:v>71</x:v>
@@ -3993,7 +3993,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P53" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q53" s="0">
         <x:v>4000</x:v>
@@ -4052,7 +4052,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q54" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R54" s="5" t="s">
         <x:v>71</x:v>
@@ -4105,7 +4105,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P55" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q55" s="0">
         <x:v>4000</x:v>
@@ -4161,7 +4161,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="P56" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q56" s="0">
         <x:v>4000</x:v>
@@ -4220,7 +4220,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q57" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R57" s="5" t="s">
         <x:v>71</x:v>
@@ -4276,7 +4276,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q58" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R58" s="5" t="s">
         <x:v>71</x:v>
@@ -4329,7 +4329,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P59" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q59" s="0">
         <x:v>4000</x:v>
@@ -4388,7 +4388,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q60" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R60" s="5" t="s">
         <x:v>71</x:v>
@@ -4441,7 +4441,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P61" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="Q61" s="0">
         <x:v>4000</x:v>
@@ -4500,7 +4500,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q62" s="0">
-        <x:v>53926</x:v>
+        <x:v>41626</x:v>
       </x:c>
       <x:c r="R62" s="5" t="s">
         <x:v>71</x:v>
@@ -4553,7 +4553,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P63" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="Q63" s="0">
         <x:v>4000</x:v>
@@ -4612,7 +4612,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q64" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="R64" s="5" t="s">
         <x:v>71</x:v>
@@ -4665,7 +4665,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P65" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="Q65" s="0">
         <x:v>4000</x:v>
@@ -4721,7 +4721,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="P66" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="Q66" s="0">
         <x:v>4000</x:v>
@@ -4780,7 +4780,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q67" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="R67" s="5" t="s">
         <x:v>71</x:v>
@@ -4836,7 +4836,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q68" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="R68" s="5" t="s">
         <x:v>71</x:v>
@@ -4889,7 +4889,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P69" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="Q69" s="0">
         <x:v>4000</x:v>
@@ -4948,7 +4948,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q70" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="R70" s="5" t="s">
         <x:v>71</x:v>
@@ -5001,7 +5001,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P71" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="Q71" s="0">
         <x:v>4000</x:v>
@@ -5060,7 +5060,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q72" s="0">
-        <x:v>56426</x:v>
+        <x:v>38222</x:v>
       </x:c>
       <x:c r="R72" s="5" t="s">
         <x:v>71</x:v>
